--- a/testdata/realdata/rrus.xlsx
+++ b/testdata/realdata/rrus.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>覆盖基站</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,6 +454,11 @@
           <t>BS-00-1651-156</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -466,6 +476,11 @@
           <t>BS-00-17676-74846003</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -483,6 +498,11 @@
           <t>BS-00-17358-6223</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -500,6 +520,11 @@
           <t>BS-00-17358-8243</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -515,6 +540,11 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>BS-11-60547-4152851</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>
